--- a/jogos_2025-09-14.xlsx
+++ b/jogos_2025-09-14.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M57" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="M62" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z62" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="M67" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N67" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.45</v>
+        <v>5.2</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="N71" t="n">
-        <v>2.85</v>
+        <v>1.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.53</v>
+        <v>2.13</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="M78" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10506,16 +10506,16 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10635,16 +10635,16 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="M85" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.41</v>
+        <v>1.19</v>
       </c>
       <c r="M90" t="n">
-        <v>3.25</v>
+        <v>5.75</v>
       </c>
       <c r="N90" t="n">
-        <v>2.65</v>
+        <v>11.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,16 +12060,16 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M99" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N99" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Z99" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="M101" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="N101" t="n">
-        <v>6.5</v>
+        <v>2.55</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="M108" t="n">
-        <v>4.77</v>
+        <v>3.8</v>
       </c>
       <c r="N108" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15162,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15549,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.26</v>
+        <v>1.9</v>
       </c>
       <c r="M121" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N121" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="M124" t="n">
         <v>3.45</v>
       </c>
       <c r="N124" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,16 +16962,16 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -17016,22 +17016,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,16 +18510,16 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,22 +18822,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19119,10 +19119,10 @@
         <v>2.85</v>
       </c>
       <c r="M145" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N145" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z145" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA145" t="n">
         <v>0</v>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="M147" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N147" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20406,13 +20406,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA155" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21354,10 +21354,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,22 +22176,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22509,10 +22509,10 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,22 +23724,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,22 +24111,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24147,13 +24147,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24186,10 +24186,10 @@
         <v>0</v>
       </c>
       <c r="Y184" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z184" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA184" t="n">
         <v>0</v>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,10 +24831,10 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,22 +25530,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,22 +25659,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,22 +25917,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,22 +26304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26340,13 +26340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26379,10 +26379,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z201" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26598,13 +26598,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26643,10 +26643,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26727,13 +26727,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -26766,10 +26766,10 @@
         <v>0</v>
       </c>
       <c r="Y204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z204" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA204" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="M216" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N216" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Z216" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M217" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N217" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z217" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="M219" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="N219" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28794,10 +28794,10 @@
         <v>1.86</v>
       </c>
       <c r="M220" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N220" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29439,10 +29439,10 @@
         <v>1.86</v>
       </c>
       <c r="M225" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N225" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>6.4</v>
+        <v>1.72</v>
       </c>
       <c r="M233" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N233" t="n">
-        <v>1.43</v>
+        <v>4.7</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z233" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33048,13 +33048,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -33087,10 +33087,10 @@
         <v>0</v>
       </c>
       <c r="Y253" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z253" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA253" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,10 +33474,10 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z256" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33822,13 +33822,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -33861,10 +33861,10 @@
         <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z259" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA259" t="n">
         <v>0</v>
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,10 +33990,10 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z260" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA260" t="n">
         <v>0</v>
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z262" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>6.4</v>
+        <v>2.25</v>
       </c>
       <c r="M264" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="N264" t="n">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="Z264" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>
@@ -34560,22 +34560,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="M265" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="N265" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,16 +34635,16 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB265" t="n">
         <v>1.62</v>
-      </c>
-      <c r="Z265" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB265" t="n">
-        <v>0</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34725,13 +34725,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34764,10 +34764,10 @@
         <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z266" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA266" t="n">
         <v>0</v>
@@ -34818,22 +34818,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34899,10 +34899,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z271" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35499,13 +35499,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="Y272" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z272" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA272" t="n">
         <v>0</v>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z277" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>8</v>
+        <v>2.18</v>
       </c>
       <c r="M278" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N278" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,16 +36312,16 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB278" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -36366,22 +36366,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,22 +36495,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36624,22 +36624,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36660,13 +36660,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>8.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -36699,10 +36699,10 @@
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z281" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,22 +36882,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="M284" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N284" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,16 +37086,16 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA284" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37785,22 +37785,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38043,22 +38043,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G294" t="n">

--- a/jogos_2025-09-14.xlsx
+++ b/jogos_2025-09-14.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M53" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="M63" t="n">
         <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="M64" t="n">
         <v>3.65</v>
       </c>
       <c r="N64" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>5.2</v>
+        <v>1.72</v>
       </c>
       <c r="M76" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10905,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N94" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.9</v>
+        <v>9.5</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="N98" t="n">
-        <v>2.55</v>
+        <v>1.32</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.9</v>
+        <v>3.13</v>
       </c>
       <c r="M100" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>4.05</v>
+        <v>2.12</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="M103" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="M107" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14646,10 +14646,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15033,10 +15033,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16581,10 +16581,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="M132" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="N132" t="n">
-        <v>2.05</v>
+        <v>3.95</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,16 +17736,16 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18951,22 +18951,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="M144" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N144" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z144" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19116,13 +19116,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="M145" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N145" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z145" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA145" t="n">
         <v>0</v>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="M148" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N148" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19761,13 +19761,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -19800,10 +19800,10 @@
         <v>0</v>
       </c>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z150" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA150" t="n">
         <v>0</v>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA157" t="n">
         <v>0</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,10 +21477,10 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,22 +21918,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,22 +22176,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,22 +23982,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24057,10 +24057,10 @@
         <v>0</v>
       </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA183" t="n">
         <v>0</v>
@@ -24111,22 +24111,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,22 +24240,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,22 +24756,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,10 +24831,10 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z189" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
@@ -25272,22 +25272,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,22 +25401,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z194" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,22 +27723,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>3.25</v>
+        <v>1.59</v>
       </c>
       <c r="M214" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="N214" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="Z214" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="M215" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N215" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z215" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M218" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N218" t="n">
-        <v>5.4</v>
+        <v>3.35</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z218" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,14 +29436,14 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="M225" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N225" t="n">
         <v>3.7</v>
       </c>
-      <c r="N225" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O225" t="n">
         <v>0</v>
       </c>
@@ -29475,16 +29475,16 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="M226" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N226" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,16 +29604,16 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.72</v>
+        <v>6.4</v>
       </c>
       <c r="M240" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N240" t="n">
-        <v>4.7</v>
+        <v>1.43</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31758,13 +31758,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -31797,10 +31797,10 @@
         <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z243" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA243" t="n">
         <v>0</v>
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32532,13 +32532,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -32571,10 +32571,10 @@
         <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z249" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA249" t="n">
         <v>0</v>
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33822,13 +33822,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -33861,10 +33861,10 @@
         <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z259" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA259" t="n">
         <v>0</v>
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,10 +33990,10 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z260" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA260" t="n">
         <v>0</v>
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z262" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="M264" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N264" t="n">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="Z264" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>
@@ -34560,22 +34560,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34641,10 +34641,10 @@
         <v>0</v>
       </c>
       <c r="AA265" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB265" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34725,13 +34725,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34764,10 +34764,10 @@
         <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z266" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA266" t="n">
         <v>0</v>
@@ -34818,22 +34818,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="M267" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N267" t="n">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,16 +34893,16 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA267" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -35205,22 +35205,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z270" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z271" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,22 +35463,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,22 +35592,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,22 +35979,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36624,22 +36624,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36660,13 +36660,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>8.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -36699,10 +36699,10 @@
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z281" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -36957,10 +36957,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37350,10 +37350,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37434,13 +37434,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z287" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA287" t="n">
         <v>0</v>
@@ -37527,22 +37527,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,22 +37656,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,22 +37785,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>2.18</v>
+        <v>1.17</v>
       </c>
       <c r="M290" t="n">
-        <v>3.45</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N290" t="n">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,16 +37860,16 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z290" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA290" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="n">
         <v>0</v>
@@ -37914,7 +37914,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z291" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38337,13 +38337,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -38370,10 +38370,10 @@
         <v>0</v>
       </c>
       <c r="W294" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X294" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y294" t="n">
         <v>0</v>
@@ -38430,22 +38430,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38698,12 +38698,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N298" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38886,10 +38886,10 @@
         <v>0</v>
       </c>
       <c r="W298" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X298" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y298" t="n">
         <v>0</v>
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39075,22 +39075,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39333,22 +39333,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G303" t="n">
